--- a/output/Data and Chart Outputs/malaysia_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/malaysia_power_capacity.xlsx
@@ -924,7 +924,7 @@
         <v>46296</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>2.532</v>
       </c>
       <c r="C2" t="n">
         <v>13.7964</v>
@@ -945,7 +945,7 @@
         <v>12.054</v>
       </c>
       <c r="I2" t="n">
-        <v>2.532</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1025,7 +1025,7 @@
         <v>46296</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>2532</v>
       </c>
       <c r="C2" t="n">
         <v>13796.4</v>
@@ -1049,7 +1049,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2532</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>29472.3</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">

--- a/output/Data and Chart Outputs/malaysia_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/malaysia_power_capacity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plants" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Monthly" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Plants" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,12 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -145,13 +146,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -176,10 +177,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -204,10 +205,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -232,10 +233,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -260,10 +261,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EDA100"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -288,10 +289,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="E87BA4"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -316,10 +317,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="008300"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -344,10 +345,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4A3AA7"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -372,10 +373,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="E34948"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -408,8 +409,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -435,8 +436,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -453,7 +454,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -467,7 +468,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -476,7 +477,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>10</col>
@@ -491,9 +492,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -825,7 +826,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -840,7 +840,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -920,7 +919,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>46296</v>
       </c>
       <c r="B2" t="n">
@@ -2437,7 +2436,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solar
+          <t xml:space="preserve">Solar
 </t>
         </is>
       </c>
@@ -2626,7 +2625,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Southern Power Generation Sdn. Bhd. (SPGP)
+          <t xml:space="preserve">Southern Power Generation Sdn. Bhd. (SPGP)
 </t>
         </is>
       </c>
@@ -2693,7 +2692,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNLS (Kerian Solar Sdn Bhd)
+          <t xml:space="preserve">KNLS (Kerian Solar Sdn Bhd)
 </t>
         </is>
       </c>
@@ -2727,7 +2726,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">MNLS (Coara Marang Sdn Bhd)
+          <t xml:space="preserve">MNLS (Coara Marang Sdn Bhd)
 </t>
         </is>
       </c>

--- a/output/Data and Chart Outputs/malaysia_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/malaysia_power_capacity.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,13 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -157,6 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Malaysia (Peninsular) installed capacity (GSO plant list) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -290,7 +290,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -318,7 +318,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -346,7 +346,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -374,7 +374,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E34948"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -826,6 +826,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -840,6 +841,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -919,7 +921,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>46296</v>
       </c>
       <c r="B2" t="n">

--- a/output/Data and Chart Outputs/malaysia_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/malaysia_power_capacity.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,12 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -826,7 +827,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -841,7 +841,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -921,7 +920,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>46296</v>
       </c>
       <c r="B2" t="n">
